--- a/docs/reports/內在價值報告_20260915.xlsx
+++ b/docs/reports/內在價值報告_20260915.xlsx
@@ -1313,25 +1313,25 @@
       </c>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="4" t="n">
-        <v>419.41</v>
+        <v>413.544</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6265.3204</v>
+        <v>6265.3256</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>539.3359</v>
+        <v>539.3558</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>5285.4917</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>-93.3</v>
+        <v>-93.40000000000001</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>25</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4698.9903</v>
+        <v>4698.9942</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>514.86</v>
+        <v>514.87</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>1600617.8442</v>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="AE10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
@@ -3369,25 +3369,25 @@
       </c>
       <c r="G23" s="8" t="inlineStr"/>
       <c r="H23" s="9" t="n">
-        <v>268.415</v>
+        <v>263.32</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>480.8061</v>
+        <v>480.8103</v>
       </c>
       <c r="J23" s="9" t="n">
         <v>9.3416</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>17.7685</v>
+        <v>17.7695</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>-44.2</v>
+        <v>-45.2</v>
       </c>
       <c r="M23" s="10" t="n">
         <v>25</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>360.6045</v>
+        <v>360.6077</v>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="AE23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF23" s="8" t="inlineStr">
@@ -4699,10 +4699,10 @@
       </c>
       <c r="G34" s="13" t="inlineStr"/>
       <c r="H34" s="14" t="n">
-        <v>384.35</v>
+        <v>377.31</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>369.4232</v>
+        <v>369.4245</v>
       </c>
       <c r="J34" s="14" t="n">
         <v>64.4277</v>
@@ -4711,13 +4711,13 @@
         <v>314.2098</v>
       </c>
       <c r="L34" s="15" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="M34" s="15" t="n">
         <v>25</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>277.0674</v>
+        <v>277.0684</v>
       </c>
       <c r="O34" s="12" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="AE34" s="12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF34" s="13" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="G44" s="23" t="inlineStr"/>
       <c r="H44" s="24" t="n">
-        <v>210.8</v>
+        <v>212.26</v>
       </c>
       <c r="I44" s="24" t="n">
         <v>45.7475</v>
@@ -5921,7 +5921,7 @@
         <v>31.5866</v>
       </c>
       <c r="L44" s="25" t="n">
-        <v>360.8</v>
+        <v>364</v>
       </c>
       <c r="M44" s="25" t="n">
         <v>25</v>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="AE44" s="22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF44" s="23" t="inlineStr">
@@ -6393,10 +6393,10 @@
       </c>
       <c r="G48" s="23" t="inlineStr"/>
       <c r="H48" s="24" t="n">
-        <v>333.08</v>
+        <v>329.27</v>
       </c>
       <c r="I48" s="24" t="n">
-        <v>49.1605</v>
+        <v>49.1607</v>
       </c>
       <c r="J48" s="24" t="n">
         <v>9.446</v>
@@ -6405,13 +6405,13 @@
         <v>34.7808</v>
       </c>
       <c r="L48" s="25" t="n">
-        <v>577.5</v>
+        <v>569.8</v>
       </c>
       <c r="M48" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N48" s="24" t="n">
-        <v>36.8704</v>
+        <v>36.8705</v>
       </c>
       <c r="O48" s="22" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="AE48" s="22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF48" s="23" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="G49" s="23" t="inlineStr"/>
       <c r="H49" s="24" t="n">
-        <v>168.91</v>
+        <v>169.93</v>
       </c>
       <c r="I49" s="24" t="n">
         <v>21.4774</v>
@@ -6527,7 +6527,7 @@
         <v>5.0403</v>
       </c>
       <c r="L49" s="25" t="n">
-        <v>686.5</v>
+        <v>691.2</v>
       </c>
       <c r="M49" s="25" t="n">
         <v>25</v>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="AE49" s="22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF49" s="23" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="G50" s="23" t="inlineStr"/>
       <c r="H50" s="24" t="n">
-        <v>503.6</v>
+        <v>501.608</v>
       </c>
       <c r="I50" s="24" t="n">
         <v>81.6729</v>
@@ -6647,7 +6647,7 @@
         <v>86.59699999999999</v>
       </c>
       <c r="L50" s="25" t="n">
-        <v>516.6</v>
+        <v>514.2</v>
       </c>
       <c r="M50" s="25" t="n">
         <v>25</v>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="AE50" s="22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF50" s="23" t="inlineStr">
@@ -6997,25 +6997,25 @@
       </c>
       <c r="G53" s="23" t="inlineStr"/>
       <c r="H53" s="24" t="n">
-        <v>1142.65</v>
+        <v>1143.77</v>
       </c>
       <c r="I53" s="24" t="n">
-        <v>544.7397999999999</v>
+        <v>544.7393</v>
       </c>
       <c r="J53" s="24" t="n">
-        <v>58.8491</v>
+        <v>58.849</v>
       </c>
       <c r="K53" s="24" t="n">
         <v>202.834</v>
       </c>
       <c r="L53" s="25" t="n">
-        <v>109.8</v>
+        <v>110</v>
       </c>
       <c r="M53" s="25" t="n">
         <v>25</v>
       </c>
       <c r="N53" s="24" t="n">
-        <v>408.5549</v>
+        <v>408.5545</v>
       </c>
       <c r="O53" s="22" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AE53" s="22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF53" s="23" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="G54" s="23" t="inlineStr"/>
       <c r="H54" s="24" t="n">
-        <v>375.305</v>
+        <v>373.775</v>
       </c>
       <c r="I54" s="24" t="n">
         <v>54.2596</v>
@@ -7131,7 +7131,7 @@
         <v>61.9902</v>
       </c>
       <c r="L54" s="25" t="n">
-        <v>591.7</v>
+        <v>588.9</v>
       </c>
       <c r="M54" s="25" t="n">
         <v>25</v>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="AE54" s="22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF54" s="23" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="G55" s="23" t="inlineStr"/>
       <c r="H55" s="24" t="n">
-        <v>252.56</v>
+        <v>248.96</v>
       </c>
       <c r="I55" s="24" t="n">
         <v>107.0856</v>
@@ -7253,7 +7253,7 @@
         <v>487.2973</v>
       </c>
       <c r="L55" s="25" t="n">
-        <v>135.8</v>
+        <v>132.5</v>
       </c>
       <c r="M55" s="25" t="n">
         <v>25</v>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AE55" s="22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF55" s="23" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="G56" s="23" t="inlineStr"/>
       <c r="H56" s="24" t="n">
-        <v>345.175</v>
+        <v>344.69</v>
       </c>
       <c r="I56" s="24" t="n">
         <v>62.856</v>
@@ -7375,7 +7375,7 @@
         <v>15.3128</v>
       </c>
       <c r="L56" s="25" t="n">
-        <v>449.2</v>
+        <v>448.4</v>
       </c>
       <c r="M56" s="25" t="n">
         <v>25</v>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="AE56" s="22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF56" s="23" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="G57" s="23" t="inlineStr"/>
       <c r="H57" s="24" t="n">
-        <v>35.095</v>
+        <v>34.435</v>
       </c>
       <c r="I57" s="24" t="n">
         <v>4.3617</v>
@@ -7497,7 +7497,7 @@
         <v>5.2053</v>
       </c>
       <c r="L57" s="25" t="n">
-        <v>704.6</v>
+        <v>689.5</v>
       </c>
       <c r="M57" s="25" t="n">
         <v>25</v>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="AE57" s="22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF57" s="23" t="inlineStr">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="G58" s="23" t="inlineStr"/>
       <c r="H58" s="24" t="n">
-        <v>109.155</v>
+        <v>108.785</v>
       </c>
       <c r="I58" s="24" t="n">
         <v>11.8315</v>
@@ -7619,7 +7619,7 @@
         <v>28.2934</v>
       </c>
       <c r="L58" s="25" t="n">
-        <v>822.6</v>
+        <v>819.5</v>
       </c>
       <c r="M58" s="25" t="n">
         <v>25</v>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="AE58" s="22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF58" s="23" t="inlineStr">
@@ -7729,10 +7729,10 @@
       </c>
       <c r="G59" s="23" t="inlineStr"/>
       <c r="H59" s="24" t="n">
-        <v>282.955</v>
+        <v>274.17</v>
       </c>
       <c r="I59" s="24" t="n">
-        <v>26.9669</v>
+        <v>26.967</v>
       </c>
       <c r="J59" s="24" t="n">
         <v>1.7995</v>
@@ -7741,7 +7741,7 @@
         <v>8.8208</v>
       </c>
       <c r="L59" s="25" t="n">
-        <v>949.3</v>
+        <v>916.7</v>
       </c>
       <c r="M59" s="25" t="n">
         <v>25</v>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="AE59" s="22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF59" s="23" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="G60" s="23" t="inlineStr"/>
       <c r="H60" s="24" t="n">
-        <v>89.185</v>
+        <v>88.47499999999999</v>
       </c>
       <c r="I60" s="24" t="n">
         <v>14.0496</v>
@@ -7863,7 +7863,7 @@
         <v>11.4611</v>
       </c>
       <c r="L60" s="25" t="n">
-        <v>534.8</v>
+        <v>529.7</v>
       </c>
       <c r="M60" s="25" t="n">
         <v>25</v>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="AE60" s="22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF60" s="23" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G61" s="23" t="inlineStr"/>
       <c r="H61" s="24" t="n">
-        <v>146.21</v>
+        <v>146.65</v>
       </c>
       <c r="I61" s="24" t="n">
         <v>20.2227</v>
@@ -7985,7 +7985,7 @@
         <v>13.4653</v>
       </c>
       <c r="L61" s="25" t="n">
-        <v>623</v>
+        <v>625.2</v>
       </c>
       <c r="M61" s="25" t="n">
         <v>25</v>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="AE61" s="22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF61" s="23" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="G66" s="23" t="inlineStr"/>
       <c r="H66" s="24" t="n">
-        <v>359.473</v>
+        <v>359.01</v>
       </c>
       <c r="I66" s="24" t="n">
         <v>4.5288</v>
@@ -8595,7 +8595,7 @@
         <v>4.6574</v>
       </c>
       <c r="L66" s="25" t="n">
-        <v>7837.5</v>
+        <v>7827.3</v>
       </c>
       <c r="M66" s="25" t="n">
         <v>25</v>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="AE66" s="22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF66" s="23" t="inlineStr">
@@ -9069,7 +9069,7 @@
         </is>
       </c>
       <c r="H70" s="29" t="n">
-        <v>135.49</v>
+        <v>131.42</v>
       </c>
       <c r="I70" s="29" t="n">
         <v>21296.5965</v>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="AE70" s="27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AF70" s="28" t="inlineStr">
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="C52" s="34" t="n">
-        <v>333.08</v>
+        <v>329.27</v>
       </c>
       <c r="D52" s="34" t="n">
-        <v>49.1605</v>
+        <v>49.1607</v>
       </c>
       <c r="E52" s="34" t="n">
         <v>9.446</v>
@@ -12252,10 +12252,10 @@
       <c r="G52" s="34" t="inlineStr"/>
       <c r="H52" s="34" t="inlineStr"/>
       <c r="I52" s="34" t="n">
-        <v>8.8996</v>
+        <v>8.9</v>
       </c>
       <c r="J52" s="34" t="n">
-        <v>12.4164</v>
+        <v>12.4165</v>
       </c>
       <c r="K52" s="34" t="n">
         <v>494.7644</v>
@@ -12293,7 +12293,7 @@
         </is>
       </c>
       <c r="C53" s="34" t="n">
-        <v>252.56</v>
+        <v>248.96</v>
       </c>
       <c r="D53" s="34" t="n">
         <v>107.0856</v>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="C54" s="34" t="n">
-        <v>514.86</v>
+        <v>514.87</v>
       </c>
       <c r="D54" s="34" t="n">
         <v>1600617.8442</v>
@@ -12395,10 +12395,10 @@
         </is>
       </c>
       <c r="C55" s="34" t="n">
-        <v>282.955</v>
+        <v>274.17</v>
       </c>
       <c r="D55" s="34" t="n">
-        <v>26.9669</v>
+        <v>26.967</v>
       </c>
       <c r="E55" s="34" t="n">
         <v>7.0983</v>
@@ -12409,7 +12409,7 @@
       <c r="G55" s="34" t="inlineStr"/>
       <c r="H55" s="34" t="inlineStr"/>
       <c r="I55" s="34" t="n">
-        <v>0.7776</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="J55" s="34" t="n">
         <v>1.7995</v>
@@ -12419,7 +12419,7 @@
       </c>
       <c r="L55" s="34" t="inlineStr"/>
       <c r="M55" s="34" t="n">
-        <v>8.789999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="N55" s="34" t="n">
         <v>8.800000000000001</v>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="C56" s="34" t="n">
-        <v>168.91</v>
+        <v>169.93</v>
       </c>
       <c r="D56" s="34" t="n">
         <v>21.4774</v>
@@ -12503,7 +12503,7 @@
         </is>
       </c>
       <c r="C57" s="34" t="n">
-        <v>345.175</v>
+        <v>344.69</v>
       </c>
       <c r="D57" s="34" t="n">
         <v>62.856</v>
@@ -12560,10 +12560,10 @@
         </is>
       </c>
       <c r="C58" s="34" t="n">
-        <v>268.415</v>
+        <v>263.32</v>
       </c>
       <c r="D58" s="34" t="n">
-        <v>480.8061</v>
+        <v>480.8103</v>
       </c>
       <c r="E58" s="34" t="n">
         <v>9.3416</v>
@@ -12574,10 +12574,10 @@
       <c r="G58" s="34" t="inlineStr"/>
       <c r="H58" s="34" t="inlineStr"/>
       <c r="I58" s="34" t="n">
-        <v>15.4536</v>
+        <v>15.4669</v>
       </c>
       <c r="J58" s="34" t="n">
-        <v>17.7685</v>
+        <v>17.7695</v>
       </c>
       <c r="K58" s="34" t="n">
         <v>6466.5299</v>
@@ -12615,7 +12615,7 @@
         </is>
       </c>
       <c r="C59" s="34" t="n">
-        <v>89.185</v>
+        <v>88.47499999999999</v>
       </c>
       <c r="D59" s="34" t="n">
         <v>14.0496</v>
@@ -12668,10 +12668,10 @@
         </is>
       </c>
       <c r="C60" s="34" t="n">
-        <v>1142.65</v>
+        <v>1143.77</v>
       </c>
       <c r="D60" s="34" t="n">
-        <v>544.7397999999999</v>
+        <v>544.7393</v>
       </c>
       <c r="E60" s="34" t="n">
         <v>83.318</v>
@@ -12682,10 +12682,10 @@
       <c r="G60" s="34" t="inlineStr"/>
       <c r="H60" s="34" t="inlineStr"/>
       <c r="I60" s="34" t="n">
-        <v>15.5374</v>
+        <v>15.5357</v>
       </c>
       <c r="J60" s="34" t="n">
-        <v>58.8491</v>
+        <v>58.849</v>
       </c>
       <c r="K60" s="34" t="n">
         <v>6600.4801</v>
@@ -12723,7 +12723,7 @@
         </is>
       </c>
       <c r="C61" s="34" t="n">
-        <v>503.6</v>
+        <v>501.608</v>
       </c>
       <c r="D61" s="34" t="n">
         <v>81.6729</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="C62" s="34" t="n">
-        <v>135.49</v>
+        <v>131.42</v>
       </c>
       <c r="D62" s="34" t="n">
         <v>21296.5965</v>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="L62" s="34" t="inlineStr"/>
       <c r="M62" s="34" t="n">
-        <v>9.42</v>
+        <v>9.4</v>
       </c>
       <c r="N62" s="34" t="n">
         <v>10.15</v>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="C63" s="34" t="n">
-        <v>210.8</v>
+        <v>212.26</v>
       </c>
       <c r="D63" s="34" t="n">
         <v>45.7475</v>
@@ -12882,7 +12882,7 @@
         </is>
       </c>
       <c r="C64" s="34" t="n">
-        <v>146.21</v>
+        <v>146.65</v>
       </c>
       <c r="D64" s="34" t="n">
         <v>20.2227</v>
@@ -12937,7 +12937,7 @@
         </is>
       </c>
       <c r="C65" s="34" t="n">
-        <v>35.095</v>
+        <v>34.435</v>
       </c>
       <c r="D65" s="34" t="n">
         <v>4.3617</v>
@@ -12992,7 +12992,7 @@
         </is>
       </c>
       <c r="C66" s="34" t="n">
-        <v>359.473</v>
+        <v>359.01</v>
       </c>
       <c r="D66" s="34" t="n">
         <v>4.5288</v>
@@ -13049,10 +13049,10 @@
         </is>
       </c>
       <c r="C67" s="34" t="n">
-        <v>419.41</v>
+        <v>413.544</v>
       </c>
       <c r="D67" s="34" t="n">
-        <v>6265.3204</v>
+        <v>6265.3256</v>
       </c>
       <c r="E67" s="34" t="n">
         <v>1397.4929</v>
@@ -13065,10 +13065,10 @@
       </c>
       <c r="H67" s="34" t="inlineStr"/>
       <c r="I67" s="34" t="n">
-        <v>539.3359</v>
+        <v>539.3558</v>
       </c>
       <c r="J67" s="34" t="n">
-        <v>905.7916</v>
+        <v>905.7939</v>
       </c>
       <c r="K67" s="34" t="n">
         <v>70736.5186</v>
@@ -13106,10 +13106,10 @@
         </is>
       </c>
       <c r="C68" s="34" t="n">
-        <v>384.35</v>
+        <v>377.31</v>
       </c>
       <c r="D68" s="34" t="n">
-        <v>369.4232</v>
+        <v>369.4245</v>
       </c>
       <c r="E68" s="34" t="n">
         <v>64.4277</v>
@@ -13120,7 +13120,7 @@
       <c r="G68" s="34" t="inlineStr"/>
       <c r="H68" s="34" t="inlineStr"/>
       <c r="I68" s="34" t="n">
-        <v>4.9352</v>
+        <v>4.9383</v>
       </c>
       <c r="J68" s="34" t="inlineStr"/>
       <c r="K68" s="34" t="n">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="L68" s="34" t="inlineStr"/>
       <c r="M68" s="34" t="n">
-        <v>8.67</v>
+        <v>8.66</v>
       </c>
       <c r="N68" s="34" t="n">
         <v>8.800000000000001</v>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="Q68" s="33" t="inlineStr">
         <is>
-          <t>{"graham_number": {"EPS(3年均)": 13.28, "BVPS": 13.892}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -22.0318, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.0771, "常態NOPAT": 6658990545.0, "WACC": 0.0867, "淨現金": -41860000000.0}, "damodaran_fcff": {"銷售/資本": 0.81, "g1": 0.11, "永續g": 0.04, "目標營業利益率": 0.0771, "WACC": 0.0867, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 1.655}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
+          <t>{"graham_number": {"EPS(3年均)": 13.28, "BVPS": 13.892}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -22.0318, "net-net買點": 0.0}, "epv": {"常態營業利益率": 0.0771, "常態NOPAT": 6658990545.0, "WACC": 0.0866, "淨現金": -41860000000.0}, "damodaran_fcff": {"銷售/資本": 0.81, "g1": 0.11, "永續g": 0.04, "目標營業利益率": 0.0771, "WACC": 0.0866, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 1.655}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
         </is>
       </c>
       <c r="C69" s="34" t="n">
-        <v>375.305</v>
+        <v>373.775</v>
       </c>
       <c r="D69" s="34" t="n">
         <v>54.2596</v>
@@ -13173,7 +13173,7 @@
       <c r="G69" s="34" t="inlineStr"/>
       <c r="H69" s="34" t="inlineStr"/>
       <c r="I69" s="34" t="n">
-        <v>4.9092</v>
+        <v>4.9093</v>
       </c>
       <c r="J69" s="34" t="n">
         <v>9.348000000000001</v>
@@ -13214,7 +13214,7 @@
         </is>
       </c>
       <c r="C70" s="34" t="n">
-        <v>109.155</v>
+        <v>108.785</v>
       </c>
       <c r="D70" s="34" t="n">
         <v>11.8315</v>
@@ -15651,22 +15651,22 @@
         </is>
       </c>
       <c r="D52" s="24" t="n">
-        <v>333.08</v>
+        <v>329.27</v>
       </c>
       <c r="E52" s="24" t="n">
         <v>24.5803</v>
       </c>
       <c r="F52" s="24" t="n">
-        <v>36.8704</v>
+        <v>36.8705</v>
       </c>
       <c r="G52" s="24" t="n">
-        <v>56.5346</v>
+        <v>56.5348</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>73.74079999999999</v>
+        <v>73.741</v>
       </c>
       <c r="I52" s="24" t="n">
-        <v>73.74079999999999</v>
+        <v>73.741</v>
       </c>
       <c r="J52" s="26" t="inlineStr">
         <is>
@@ -15674,10 +15674,10 @@
         </is>
       </c>
       <c r="K52" s="24" t="n">
-        <v>6.7754</v>
+        <v>6.6978</v>
       </c>
       <c r="L52" s="24" t="n">
-        <v>36.8704</v>
+        <v>36.8705</v>
       </c>
     </row>
     <row r="53">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="D53" s="24" t="n">
-        <v>252.56</v>
+        <v>248.96</v>
       </c>
       <c r="E53" s="24" t="n">
         <v>53.5428</v>
@@ -15720,7 +15720,7 @@
         </is>
       </c>
       <c r="K53" s="24" t="n">
-        <v>2.3585</v>
+        <v>2.3249</v>
       </c>
       <c r="L53" s="24" t="n">
         <v>80.3142</v>
@@ -15743,7 +15743,7 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>514.86</v>
+        <v>514.87</v>
       </c>
       <c r="E54" s="4" t="n">
         <v>800308.9221</v>
@@ -15789,7 +15789,7 @@
         </is>
       </c>
       <c r="D55" s="24" t="n">
-        <v>282.955</v>
+        <v>274.17</v>
       </c>
       <c r="E55" s="24" t="n">
         <v>13.4835</v>
@@ -15812,7 +15812,7 @@
         </is>
       </c>
       <c r="K55" s="24" t="n">
-        <v>10.4927</v>
+        <v>10.1669</v>
       </c>
       <c r="L55" s="24" t="n">
         <v>20.2252</v>
@@ -15835,7 +15835,7 @@
         </is>
       </c>
       <c r="D56" s="24" t="n">
-        <v>168.91</v>
+        <v>169.93</v>
       </c>
       <c r="E56" s="24" t="n">
         <v>10.7387</v>
@@ -15858,7 +15858,7 @@
         </is>
       </c>
       <c r="K56" s="24" t="n">
-        <v>7.8646</v>
+        <v>7.9121</v>
       </c>
       <c r="L56" s="24" t="n">
         <v>16.108</v>
@@ -15881,7 +15881,7 @@
         </is>
       </c>
       <c r="D57" s="24" t="n">
-        <v>345.175</v>
+        <v>344.69</v>
       </c>
       <c r="E57" s="24" t="n">
         <v>31.428</v>
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="K57" s="24" t="n">
-        <v>5.4915</v>
+        <v>5.4838</v>
       </c>
       <c r="L57" s="24" t="n">
         <v>47.142</v>
@@ -15927,22 +15927,22 @@
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>268.415</v>
+        <v>263.32</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>240.403</v>
+        <v>240.4051</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>360.6045</v>
+        <v>360.6077</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>552.927</v>
+        <v>552.9318</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>721.2091</v>
+        <v>721.2154</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>721.2091</v>
+        <v>721.2154</v>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
@@ -15950,10 +15950,10 @@
         </is>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.5583</v>
+        <v>0.5477</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>360.6045</v>
+        <v>360.6077</v>
       </c>
     </row>
     <row r="59">
@@ -15973,7 +15973,7 @@
         </is>
       </c>
       <c r="D59" s="24" t="n">
-        <v>89.185</v>
+        <v>88.47499999999999</v>
       </c>
       <c r="E59" s="24" t="n">
         <v>7.0248</v>
@@ -15996,7 +15996,7 @@
         </is>
       </c>
       <c r="K59" s="24" t="n">
-        <v>6.3479</v>
+        <v>6.2973</v>
       </c>
       <c r="L59" s="24" t="n">
         <v>10.5372</v>
@@ -16019,22 +16019,22 @@
         </is>
       </c>
       <c r="D60" s="24" t="n">
-        <v>1142.65</v>
+        <v>1143.77</v>
       </c>
       <c r="E60" s="24" t="n">
-        <v>272.3699</v>
+        <v>272.3696</v>
       </c>
       <c r="F60" s="24" t="n">
-        <v>408.5549</v>
+        <v>408.5545</v>
       </c>
       <c r="G60" s="24" t="n">
-        <v>626.4508</v>
+        <v>626.4502</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>817.1097</v>
+        <v>817.1088999999999</v>
       </c>
       <c r="I60" s="24" t="n">
-        <v>817.1097</v>
+        <v>817.1088999999999</v>
       </c>
       <c r="J60" s="26" t="inlineStr">
         <is>
@@ -16042,10 +16042,10 @@
         </is>
       </c>
       <c r="K60" s="24" t="n">
-        <v>2.0976</v>
+        <v>2.0997</v>
       </c>
       <c r="L60" s="24" t="n">
-        <v>408.5549</v>
+        <v>408.5545</v>
       </c>
     </row>
     <row r="61">
@@ -16065,10 +16065,10 @@
         </is>
       </c>
       <c r="D61" s="24" t="n">
-        <v>503.6</v>
+        <v>501.608</v>
       </c>
       <c r="E61" s="24" t="n">
-        <v>40.8364</v>
+        <v>40.8365</v>
       </c>
       <c r="F61" s="24" t="n">
         <v>61.2547</v>
@@ -16077,10 +16077,10 @@
         <v>93.9238</v>
       </c>
       <c r="H61" s="24" t="n">
-        <v>122.5093</v>
+        <v>122.5094</v>
       </c>
       <c r="I61" s="24" t="n">
-        <v>122.5093</v>
+        <v>122.5094</v>
       </c>
       <c r="J61" s="26" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         </is>
       </c>
       <c r="K61" s="24" t="n">
-        <v>6.1661</v>
+        <v>6.1417</v>
       </c>
       <c r="L61" s="24" t="n">
         <v>61.2547</v>
@@ -16111,7 +16111,7 @@
         </is>
       </c>
       <c r="D62" s="29" t="n">
-        <v>135.49</v>
+        <v>131.42</v>
       </c>
       <c r="E62" s="29" t="n">
         <v>10648.2983</v>
@@ -16134,7 +16134,7 @@
         </is>
       </c>
       <c r="K62" s="29" t="n">
-        <v>0.0064</v>
+        <v>0.0062</v>
       </c>
       <c r="L62" s="29" t="n">
         <v>15972.4474</v>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="D63" s="24" t="n">
-        <v>210.8</v>
+        <v>212.26</v>
       </c>
       <c r="E63" s="24" t="n">
         <v>22.8737</v>
@@ -16180,7 +16180,7 @@
         </is>
       </c>
       <c r="K63" s="24" t="n">
-        <v>4.6079</v>
+        <v>4.6398</v>
       </c>
       <c r="L63" s="24" t="n">
         <v>34.3106</v>
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="D64" s="24" t="n">
-        <v>146.21</v>
+        <v>146.65</v>
       </c>
       <c r="E64" s="24" t="n">
         <v>10.1114</v>
@@ -16226,7 +16226,7 @@
         </is>
       </c>
       <c r="K64" s="24" t="n">
-        <v>7.23</v>
+        <v>7.2518</v>
       </c>
       <c r="L64" s="24" t="n">
         <v>15.167</v>
@@ -16249,7 +16249,7 @@
         </is>
       </c>
       <c r="D65" s="24" t="n">
-        <v>35.095</v>
+        <v>34.435</v>
       </c>
       <c r="E65" s="24" t="n">
         <v>2.1808</v>
@@ -16272,7 +16272,7 @@
         </is>
       </c>
       <c r="K65" s="24" t="n">
-        <v>8.046200000000001</v>
+        <v>7.8949</v>
       </c>
       <c r="L65" s="24" t="n">
         <v>3.2713</v>
@@ -16295,7 +16295,7 @@
         </is>
       </c>
       <c r="D66" s="24" t="n">
-        <v>359.473</v>
+        <v>359.01</v>
       </c>
       <c r="E66" s="24" t="n">
         <v>2.2644</v>
@@ -16318,7 +16318,7 @@
         </is>
       </c>
       <c r="K66" s="24" t="n">
-        <v>79.37520000000001</v>
+        <v>79.27290000000001</v>
       </c>
       <c r="L66" s="24" t="n">
         <v>3.3966</v>
@@ -16341,22 +16341,22 @@
         </is>
       </c>
       <c r="D67" s="4" t="n">
-        <v>419.41</v>
+        <v>413.544</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>3132.6602</v>
+        <v>3132.6628</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>4698.9903</v>
+        <v>4698.9942</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>7205.1184</v>
+        <v>7205.1244</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>9397.980600000001</v>
+        <v>9397.9884</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>9397.980600000001</v>
+        <v>9397.9884</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -16364,10 +16364,10 @@
         </is>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0.0669</v>
+        <v>0.066</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>4698.9903</v>
+        <v>4698.9942</v>
       </c>
     </row>
     <row r="68">
@@ -16387,22 +16387,22 @@
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>384.35</v>
+        <v>377.31</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>184.7116</v>
+        <v>184.7123</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>277.0674</v>
+        <v>277.0684</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>424.8367</v>
+        <v>424.8382</v>
       </c>
       <c r="H68" s="14" t="n">
-        <v>554.1348</v>
+        <v>554.1368</v>
       </c>
       <c r="I68" s="14" t="n">
-        <v>554.1348</v>
+        <v>554.1368</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
@@ -16410,10 +16410,10 @@
         </is>
       </c>
       <c r="K68" s="14" t="n">
-        <v>1.0404</v>
+        <v>1.0213</v>
       </c>
       <c r="L68" s="14" t="n">
-        <v>277.0674</v>
+        <v>277.0684</v>
       </c>
     </row>
     <row r="69">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="D69" s="24" t="n">
-        <v>375.305</v>
+        <v>373.775</v>
       </c>
       <c r="E69" s="24" t="n">
         <v>27.1298</v>
@@ -16442,7 +16442,7 @@
         <v>40.6947</v>
       </c>
       <c r="G69" s="24" t="n">
-        <v>62.3985</v>
+        <v>62.3986</v>
       </c>
       <c r="H69" s="24" t="n">
         <v>81.38939999999999</v>
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="K69" s="24" t="n">
-        <v>6.9168</v>
+        <v>6.8886</v>
       </c>
       <c r="L69" s="24" t="n">
         <v>40.6947</v>
@@ -16479,7 +16479,7 @@
         </is>
       </c>
       <c r="D70" s="24" t="n">
-        <v>109.155</v>
+        <v>108.785</v>
       </c>
       <c r="E70" s="24" t="n">
         <v>5.9158</v>
@@ -16502,7 +16502,7 @@
         </is>
       </c>
       <c r="K70" s="24" t="n">
-        <v>9.2258</v>
+        <v>9.1945</v>
       </c>
       <c r="L70" s="24" t="n">
         <v>8.873699999999999</v>
